--- a/input_data/sna_country_data/URY/cei.xlsx
+++ b/input_data/sna_country_data/URY/cei.xlsx
@@ -13,13 +13,14 @@
     <sheet name="2019" sheetId="5" r:id="rId7"/>
     <sheet name="2020" sheetId="6" r:id="rId8"/>
     <sheet name="2021" sheetId="7" r:id="rId9"/>
+    <sheet name="2022" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10414" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11070" uniqueCount="76">
   <si>
     <t>code</t>
   </si>
@@ -865,10 +866,10 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
+        <v>-3264.8749993161591</v>
+      </c>
+      <c r="F27" s="1">
         <v>-3264.8749993161441</v>
-      </c>
-      <c r="F27" s="1">
-        <v>-3264.8749993161591</v>
       </c>
       <c r="G27" s="1">
         <v>65128.014697722727</v>
@@ -945,10 +946,10 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
+        <v>-3264.8749993161441</v>
+      </c>
+      <c r="F31" s="1">
         <v>-3264.8749993161591</v>
-      </c>
-      <c r="F31" s="1">
-        <v>-3264.8749993161441</v>
       </c>
       <c r="G31" s="1">
         <v>65128.014697722727</v>
@@ -1019,10 +1020,10 @@
         <v>-25147.551874929632</v>
       </c>
       <c r="G34" s="1">
-        <v>25446.753598644849</v>
+        <v>25446.753598644718</v>
       </c>
       <c r="H34" s="1">
-        <v>25446.753598644849</v>
+        <v>25446.753598644718</v>
       </c>
     </row>
     <row r="35">
@@ -1045,63 +1046,63 @@
         <v>-25147.551874929632</v>
       </c>
       <c r="G35" s="1">
-        <v>25446.753598644718</v>
+        <v>25446.753598644849</v>
       </c>
       <c r="H35" s="1">
-        <v>25446.753598644718</v>
+        <v>25446.753598644849</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>79482.446760280014</v>
-      </c>
-      <c r="F36" s="1">
-        <v>79482.446760280014</v>
-      </c>
+        <v>926.5806651800001</v>
+      </c>
+      <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>113976.0975413</v>
-      </c>
-      <c r="F37" s="1"/>
+        <v>79482.446760280014</v>
+      </c>
+      <c r="F37" s="1">
+        <v>79482.446760280014</v>
+      </c>
       <c r="G37" s="1"/>
-      <c r="H37" s="1">
-        <v>137582.86030768359</v>
-      </c>
+      <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>926.5806651800001</v>
+        <v>113976.0975413</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+      <c r="H38" s="1">
+        <v>137582.86030768359</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
@@ -1687,7 +1688,7 @@
         <v>-10570.43407502865</v>
       </c>
       <c r="F27" s="1">
-        <v>-10570.43407502865</v>
+        <v>-10570.434075028639</v>
       </c>
       <c r="G27" s="1">
         <v>124508.5573505638</v>
@@ -1767,7 +1768,7 @@
         <v>-10570.434075028639</v>
       </c>
       <c r="F31" s="1">
-        <v>-10570.434075028639</v>
+        <v>-10570.43407502865</v>
       </c>
       <c r="G31" s="1">
         <v>124508.5573505638</v>
@@ -1831,7 +1832,7 @@
         <v>-14574.43484844782</v>
       </c>
       <c r="D34" s="1">
-        <v>-14574.434848447811</v>
+        <v>-14574.43484844782</v>
       </c>
       <c r="E34" s="1">
         <v>-66950.582658753847</v>
@@ -1840,10 +1841,10 @@
         <v>-66950.582658753861</v>
       </c>
       <c r="G34" s="1">
-        <v>55330.055140544151</v>
+        <v>55330.055140544697</v>
       </c>
       <c r="H34" s="1">
-        <v>55330.055140544151</v>
+        <v>55330.055140544697</v>
       </c>
     </row>
     <row r="35">
@@ -1857,7 +1858,7 @@
         <v>-14574.434848447811</v>
       </c>
       <c r="D35" s="1">
-        <v>-14574.43484844782</v>
+        <v>-14574.434848447811</v>
       </c>
       <c r="E35" s="1">
         <v>-66950.582658753861</v>
@@ -1866,63 +1867,63 @@
         <v>-66950.582658753847</v>
       </c>
       <c r="G35" s="1">
-        <v>55330.055140544697</v>
+        <v>55330.055140544151</v>
       </c>
       <c r="H35" s="1">
-        <v>55330.055140544697</v>
+        <v>55330.055140544151</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>181558.9914336357</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1">
-        <v>310.92989817709997</v>
-      </c>
-      <c r="H36" s="1">
-        <v>223683.25268700649</v>
-      </c>
+        <v>147042.35994689999</v>
+      </c>
+      <c r="F36" s="1">
+        <v>147042.21094677999</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>1410.7265588499999</v>
+        <v>181558.9914336357</v>
       </c>
       <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="G37" s="1">
+        <v>310.92989817709997</v>
+      </c>
+      <c r="H37" s="1">
+        <v>223683.25268700649</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>147042.35994689999</v>
-      </c>
-      <c r="F38" s="1">
-        <v>147042.21094677999</v>
-      </c>
+        <v>1410.7265588499999</v>
+      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -2509,7 +2510,7 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
-        <v>-25017.38878234318</v>
+        <v>-25017.388782343201</v>
       </c>
       <c r="F27" s="1">
         <v>-25017.388782343201</v>
@@ -2589,7 +2590,7 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
-        <v>-25017.388782343201</v>
+        <v>-25017.38878234318</v>
       </c>
       <c r="F31" s="1">
         <v>-25017.38878234318</v>
@@ -2656,10 +2657,10 @@
         <v>-4009.0753441289771</v>
       </c>
       <c r="D34" s="1">
-        <v>-4009.0753441289712</v>
+        <v>-4009.0753441289771</v>
       </c>
       <c r="E34" s="1">
-        <v>-63565.818181042087</v>
+        <v>-63565.770979082881</v>
       </c>
       <c r="F34" s="1">
         <v>-63565.770979082881</v>
@@ -2682,10 +2683,10 @@
         <v>-4009.0753441289712</v>
       </c>
       <c r="D35" s="1">
-        <v>-4009.0753441289771</v>
+        <v>-4009.0753441289712</v>
       </c>
       <c r="E35" s="1">
-        <v>-63565.770979082881</v>
+        <v>-63565.818181042087</v>
       </c>
       <c r="F35" s="1">
         <v>-63565.818181042087</v>
@@ -2699,55 +2700,55 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>201604.21968480741</v>
+        <v>1378.685344355712</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" s="1">
-        <v>337.34758922499998</v>
-      </c>
-      <c r="H36" s="1">
-        <v>253381.7166756459</v>
-      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>170013.75605207999</v>
-      </c>
-      <c r="F37" s="1">
-        <v>170013.75605207999</v>
-      </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+        <v>201604.21968480741</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1">
+        <v>337.34758922499998</v>
+      </c>
+      <c r="H37" s="1">
+        <v>253381.7166756459</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>1378.685344355712</v>
-      </c>
-      <c r="F38" s="1"/>
+        <v>170013.75605207999</v>
+      </c>
+      <c r="F38" s="1">
+        <v>170013.75605207999</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -3481,13 +3482,13 @@
         <v>-49773.892247342999</v>
       </c>
       <c r="F34" s="1">
-        <v>-49773.892247343349</v>
+        <v>-49773.892247342999</v>
       </c>
       <c r="G34" s="1">
         <v>33283.712597372418</v>
       </c>
       <c r="H34" s="1">
-        <v>33283.712597372112</v>
+        <v>33283.712597372418</v>
       </c>
     </row>
     <row r="35">
@@ -3507,13 +3508,13 @@
         <v>-49773.892247343349</v>
       </c>
       <c r="F35" s="1">
-        <v>-49773.892247342999</v>
+        <v>-49773.892247343349</v>
       </c>
       <c r="G35" s="1">
         <v>33283.712597372112</v>
       </c>
       <c r="H35" s="1">
-        <v>33283.712597372418</v>
+        <v>33283.712597372112</v>
       </c>
     </row>
     <row r="36">
@@ -4151,10 +4152,10 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
+        <v>-47487.012322160852</v>
+      </c>
+      <c r="F27" s="1">
         <v>-47487.012322160823</v>
-      </c>
-      <c r="F27" s="1">
-        <v>-47487.012322160852</v>
       </c>
       <c r="G27" s="1">
         <v>137422.3722114753</v>
@@ -4229,10 +4230,10 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
+        <v>-47487.012322160823</v>
+      </c>
+      <c r="F31" s="1">
         <v>-47487.012322160852</v>
-      </c>
-      <c r="F31" s="1">
-        <v>-47487.012322160823</v>
       </c>
       <c r="G31" s="1">
         <v>137422.3722114753</v>
@@ -4302,10 +4303,10 @@
         <v>-63947.039175030113</v>
       </c>
       <c r="F34" s="1">
-        <v>-63947.039175029808</v>
+        <v>-63947.039175030113</v>
       </c>
       <c r="G34" s="1">
-        <v>39248.472782472847</v>
+        <v>39248.472782472993</v>
       </c>
       <c r="H34" s="1">
         <v>39248.472782472847</v>
@@ -4328,10 +4329,10 @@
         <v>-63947.039175029808</v>
       </c>
       <c r="F35" s="1">
-        <v>-63947.039175030113</v>
+        <v>-63947.039175029808</v>
       </c>
       <c r="G35" s="1">
-        <v>39248.472782472993</v>
+        <v>39248.472782472847</v>
       </c>
       <c r="H35" s="1">
         <v>39248.472782472993</v>
@@ -4339,57 +4340,57 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>239376.743428952</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1">
-        <v>402.67289956090139</v>
-      </c>
-      <c r="H36" s="1">
-        <v>298520.24294644757</v>
-      </c>
+        <v>200663.39336498949</v>
+      </c>
+      <c r="F36" s="1">
+        <v>200663.39336498949</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>200663.39336498949</v>
-      </c>
-      <c r="F37" s="1">
-        <v>200663.39336498949</v>
-      </c>
+        <v>1691.532447066628</v>
+      </c>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>1691.532447066628</v>
+        <v>239376.743428952</v>
       </c>
       <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+      <c r="G38" s="1">
+        <v>402.67289956090139</v>
+      </c>
+      <c r="H38" s="1">
+        <v>298520.24294644757</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
@@ -5113,7 +5114,7 @@
         <v>10171.468589380889</v>
       </c>
       <c r="D34" s="1">
-        <v>10171.459058987501</v>
+        <v>10171.468589380889</v>
       </c>
       <c r="E34" s="1">
         <v>-79545.106801385089</v>
@@ -5122,7 +5123,7 @@
         <v>-79545.106801385089</v>
       </c>
       <c r="G34" s="1">
-        <v>66058.729479423899</v>
+        <v>66059.10105946564</v>
       </c>
       <c r="H34" s="1">
         <v>66058.729479423899</v>
@@ -5139,7 +5140,7 @@
         <v>10171.459058987501</v>
       </c>
       <c r="D35" s="1">
-        <v>10171.468589380889</v>
+        <v>10171.459058987501</v>
       </c>
       <c r="E35" s="1">
         <v>-79545.106801385089</v>
@@ -5148,7 +5149,7 @@
         <v>-79545.106801385089</v>
       </c>
       <c r="G35" s="1">
-        <v>66059.10105946564</v>
+        <v>66058.729479423899</v>
       </c>
       <c r="H35" s="1">
         <v>66059.10105946564</v>
@@ -5156,57 +5157,57 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>250754.8245620098</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1">
-        <v>442.30808405340002</v>
-      </c>
-      <c r="H36" s="1">
-        <v>313181.58741649322</v>
-      </c>
+        <v>242248.42014405999</v>
+      </c>
+      <c r="F36" s="1">
+        <v>242248.42014405999</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>242248.42014405999</v>
-      </c>
-      <c r="F37" s="1">
-        <v>242248.42014405999</v>
-      </c>
+        <v>1625.492093275358</v>
+      </c>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>1625.492093275358</v>
+        <v>250754.8245620098</v>
       </c>
       <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+      <c r="G38" s="1">
+        <v>442.30808405340002</v>
+      </c>
+      <c r="H38" s="1">
+        <v>313181.58741649322</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
@@ -5790,7 +5791,7 @@
         <v>-25100.98923128075</v>
       </c>
       <c r="F27" s="1">
-        <v>-25100.989231280721</v>
+        <v>-25100.98923128075</v>
       </c>
       <c r="G27" s="1">
         <v>147140.71535390709</v>
@@ -5868,7 +5869,7 @@
         <v>-25100.989231280721</v>
       </c>
       <c r="F31" s="1">
-        <v>-25100.98923128075</v>
+        <v>-25100.989231280721</v>
       </c>
       <c r="G31" s="1">
         <v>147140.71535390709</v>
@@ -5932,7 +5933,7 @@
         <v>63134.524836636163</v>
       </c>
       <c r="D34" s="1">
-        <v>63134.515306242713</v>
+        <v>63134.524836636163</v>
       </c>
       <c r="E34" s="1">
         <v>-60032.164387225363</v>
@@ -5941,10 +5942,10 @@
         <v>-60032.164387225363</v>
       </c>
       <c r="G34" s="1">
+        <v>50492.474199901873</v>
+      </c>
+      <c r="H34" s="1">
         <v>50492.474199902237</v>
-      </c>
-      <c r="H34" s="1">
-        <v>50492.474199901873</v>
       </c>
     </row>
     <row r="35">
@@ -5958,7 +5959,7 @@
         <v>63134.515306242713</v>
       </c>
       <c r="D35" s="1">
-        <v>63134.524836636163</v>
+        <v>63134.515306242713</v>
       </c>
       <c r="E35" s="1">
         <v>-60032.164387225363</v>
@@ -5967,10 +5968,829 @@
         <v>-60032.164387225363</v>
       </c>
       <c r="G35" s="1">
+        <v>50492.474199902237</v>
+      </c>
+      <c r="H35" s="1">
         <v>50492.474199901873</v>
       </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1">
+        <v>272538.25067318691</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1">
+        <v>456.40441621169998</v>
+      </c>
+      <c r="H36" s="1">
+        <v>335741.85541967727</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1">
+        <v>1891.473003789004</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1">
+        <v>264574.52162751998</v>
+      </c>
+      <c r="F38" s="1">
+        <v>264574.52162751998</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1">
+        <v>-163664.28456680939</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-163664.28456680939</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1">
+        <v>285323.40139903611</v>
+      </c>
+      <c r="F3" s="1">
+        <v>285323.40139903611</v>
+      </c>
+      <c r="G3" s="1">
+        <v>553078.09513065405</v>
+      </c>
+      <c r="H3" s="1">
+        <v>553078.09513065405</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1">
+        <v>384970.1030054891</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1861.6912202219751</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1">
+        <v>21682.436782327299</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1">
+        <v>341955.59309482371</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1">
+        <v>43014.509910665402</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1861.6912202219751</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
+        <v>21682.436782327299</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>-26899.506842827399</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <v>-3925.6933279999998</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>-22973.81351482739</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1">
+        <v>223434.52756392289</v>
+      </c>
+      <c r="H10" s="1">
+        <v>223434.52756392289</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1">
+        <v>-971.71534134324588</v>
+      </c>
+      <c r="F11" s="1">
+        <v>-971.71534134324588</v>
+      </c>
+      <c r="G11" s="1">
+        <v>237783.7980568129</v>
+      </c>
+      <c r="H11" s="1">
+        <v>237783.7980568129</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="1">
+        <v>-166.16255443767179</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>284433.42552015733</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1198857.028720302</v>
+      </c>
+      <c r="H12" s="1">
+        <v>70177.332727590896</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="1">
+        <v>332407.8169108135</v>
+      </c>
+      <c r="D13" s="1">
+        <v>62000.935867956527</v>
+      </c>
+      <c r="E13" s="1">
+        <v>40258.144947410867</v>
+      </c>
+      <c r="F13" s="1">
+        <v>73528.302583514946</v>
+      </c>
+      <c r="G13" s="1">
+        <v>306643.64357360499</v>
+      </c>
+      <c r="H13" s="1">
+        <v>29892.73058249613</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="1">
+        <v>54537.954693713851</v>
+      </c>
+      <c r="D14" s="1">
+        <v>35792.240283027109</v>
+      </c>
+      <c r="E14" s="1">
+        <v>13114.56647114071</v>
+      </c>
+      <c r="F14" s="1">
+        <v>73528.302583514946</v>
+      </c>
+      <c r="G14" s="1">
+        <v>20805.4458750786</v>
+      </c>
+      <c r="H14" s="1">
+        <v>29892.73058249613</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="1">
+        <v>277869.86221709958</v>
+      </c>
+      <c r="D15" s="1">
+        <v>26208.695584929421</v>
+      </c>
+      <c r="E15" s="1">
+        <v>27143.578476270159</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1">
+        <v>285838.19769852638</v>
+      </c>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="1">
+        <v>270240.71848841931</v>
+      </c>
+      <c r="D16" s="1">
+        <v>270240.71848841931</v>
+      </c>
+      <c r="E16" s="1">
+        <v>323828.72318521439</v>
+      </c>
+      <c r="F16" s="1">
+        <v>323828.72318521439</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1936826.2673321471</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1936826.2673321471</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="1">
+        <v>989.03254398977413</v>
+      </c>
+      <c r="D17" s="1">
+        <v>11205.3050997301</v>
+      </c>
+      <c r="E17" s="1">
+        <v>245083.52661911721</v>
+      </c>
+      <c r="F17" s="1">
+        <v>32.138723151999997</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1">
+        <v>128516.9430967318</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2136.620351999999</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1">
+        <v>304097.67081209831</v>
+      </c>
+      <c r="F18" s="1">
+        <v>396636.94692928862</v>
+      </c>
+      <c r="G18" s="1">
+        <v>423096.35907884262</v>
+      </c>
+      <c r="H18" s="1">
+        <v>380673.27105001023</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2136.620351999999</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1">
+        <v>396636.94692928862</v>
+      </c>
+      <c r="G19" s="1">
+        <v>422682.82670530392</v>
+      </c>
+      <c r="H19" s="1">
+        <v>413.53237353870003</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="1">
+        <v>25218.060103548811</v>
+      </c>
+      <c r="D20" s="1">
+        <v>23378.532722230819</v>
+      </c>
+      <c r="E20" s="1">
+        <v>283043.81914846302</v>
+      </c>
+      <c r="F20" s="1">
+        <v>301615.55855578999</v>
+      </c>
+      <c r="G20" s="1">
+        <v>77097.011153930551</v>
+      </c>
+      <c r="H20" s="1">
+        <v>79491.170462897542</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.98468900000000004</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2209.45150165</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1">
+        <v>501.43877443124518</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1">
+        <v>6677.4237772516326</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2209.45150165</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1">
+        <v>645.39812603445682</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1">
+        <v>8444.6193177867972</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1778.2417582882031</v>
+      </c>
+      <c r="D23" s="1">
+        <v>51.931445999999987</v>
+      </c>
+      <c r="E23" s="1">
+        <v>51.931446000000001</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1778.2417582882031</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="1">
+        <v>21229.382154610608</v>
+      </c>
+      <c r="D24" s="1">
+        <v>21117.149774580819</v>
+      </c>
+      <c r="E24" s="1">
+        <v>10874.73278740322</v>
+      </c>
+      <c r="F24" s="1">
+        <v>29503.269254045339</v>
+      </c>
+      <c r="G24" s="1">
+        <v>68652.391836143754</v>
+      </c>
+      <c r="H24" s="1">
+        <v>72813.746685645907</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="1">
+        <v>264000.59366599697</v>
+      </c>
+      <c r="D25" s="1">
+        <v>264000.59366599697</v>
+      </c>
+      <c r="E25" s="1">
+        <v>457769.09555666213</v>
+      </c>
+      <c r="F25" s="1">
+        <v>457769.09555666213</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1848338.25295528</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1848338.25295528</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1">
+        <v>47979.567736357872</v>
+      </c>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1">
+        <v>-14925.349563662399</v>
+      </c>
+      <c r="F27" s="1">
+        <v>-14925.349563662399</v>
+      </c>
+      <c r="G27" s="1">
+        <v>154708.9272309329</v>
+      </c>
+      <c r="H27" s="1">
+        <v>154708.9272309329</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1">
+        <v>277480.29466432339</v>
+      </c>
+      <c r="G28" s="1">
+        <v>286584.62147938652</v>
+      </c>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1">
+        <v>180288.80089233871</v>
+      </c>
+      <c r="F29" s="1">
+        <v>180288.80089233871</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2134922.8744346672</v>
+      </c>
+      <c r="H29" s="1">
+        <v>2134922.8744346672</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1">
+        <v>47979.567736357872</v>
+      </c>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1">
+        <v>-14925.34956366237</v>
+      </c>
+      <c r="F31" s="1">
+        <v>-14925.34956366237</v>
+      </c>
+      <c r="G31" s="1">
+        <v>154708.9272309329</v>
+      </c>
+      <c r="H31" s="1">
+        <v>154708.9272309329</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="1">
+        <v>100336.30909918759</v>
+      </c>
+      <c r="D32" s="1">
+        <v>100336.30909918759</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="1">
+        <v>6</v>
+      </c>
+      <c r="D33" s="1">
+        <v>-511.08080334355799</v>
+      </c>
+      <c r="E33" s="1">
+        <v>6377.3810400000002</v>
+      </c>
+      <c r="F33" s="1">
+        <v>-16638.95979700649</v>
+      </c>
+      <c r="G33" s="1">
+        <v>10825.379000006489</v>
+      </c>
+      <c r="H33" s="1">
+        <v>-2637.2212589999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="1">
+        <v>100042.56091099371</v>
+      </c>
+      <c r="D34" s="1">
+        <v>100042.56091099371</v>
+      </c>
+      <c r="E34" s="1">
+        <v>-77960.495719855215</v>
+      </c>
+      <c r="F34" s="1">
+        <v>-77960.495719855215</v>
+      </c>
+      <c r="G34" s="1">
+        <v>41496.633402731371</v>
+      </c>
+      <c r="H34" s="1">
+        <v>41496.633402731371</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="1">
+        <v>100042.5513806003</v>
+      </c>
+      <c r="D35" s="1">
+        <v>100042.5513806003</v>
+      </c>
+      <c r="E35" s="1">
+        <v>-77960.495719855215</v>
+      </c>
+      <c r="F35" s="1">
+        <v>-77960.495719855215</v>
+      </c>
+      <c r="G35" s="1">
+        <v>41496.722438386299</v>
+      </c>
       <c r="H35" s="1">
-        <v>50492.474199902237</v>
+        <v>41496.722438386299</v>
       </c>
     </row>
     <row r="36">
@@ -5983,10 +6803,10 @@
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>264574.52162751998</v>
+        <v>269832.6087690253</v>
       </c>
       <c r="F36" s="1">
-        <v>264574.52162751998</v>
+        <v>269832.6087690253</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -6001,14 +6821,14 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>272538.25067318691</v>
+        <v>304097.67081209831</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1">
-        <v>456.40441621169998</v>
+        <v>413.53237353870003</v>
       </c>
       <c r="H37" s="1">
-        <v>335741.85541967727</v>
+        <v>380259.73867647152</v>
       </c>
     </row>
     <row r="38">
@@ -6021,7 +6841,7 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>1891.473003789004</v>
+        <v>1639.1480200000001</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
